--- a/Bao cao/HCM/HCM_Model_2026-07-11.xlsx
+++ b/Bao cao/HCM/HCM_Model_2026-07-11.xlsx
@@ -13924,15 +13924,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13953,7 +13958,7 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>DT Tự doanh (net)</t>
+          <t>DT Tự doanh (FVTPL+AFS)</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
@@ -13962,6 +13967,31 @@
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>DT QLQ (ước tính)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>LNG Môi giới</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>LNG Margin</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>LNG Tự doanh</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>LNG IB+Lưu ký</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>LNST</t>
         </is>
@@ -13986,6 +14016,21 @@
         <v>60.1</v>
       </c>
       <c r="F2" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>147.3</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>156.3</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>146.7</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="K2" s="13" t="n">
         <v>324.6</v>
       </c>
     </row>
@@ -14008,6 +14053,21 @@
         <v>5.5</v>
       </c>
       <c r="F3" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>136.2</v>
+      </c>
+      <c r="I3" s="13" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="J3" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K3" s="13" t="n">
         <v>147.2</v>
       </c>
     </row>
@@ -14030,6 +14090,21 @@
         <v>55</v>
       </c>
       <c r="F4" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="K4" s="13" t="n">
         <v>131.5</v>
       </c>
     </row>
@@ -14052,6 +14127,21 @@
         <v>7.2</v>
       </c>
       <c r="F5" s="13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K5" s="13" t="n">
         <v>72.09999999999999</v>
       </c>
     </row>
@@ -14074,6 +14164,21 @@
         <v>3.9</v>
       </c>
       <c r="F6" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="K6" s="13" t="n">
         <v>82</v>
       </c>
     </row>
@@ -14096,6 +14201,21 @@
         <v>34.7</v>
       </c>
       <c r="F7" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="K7" s="13" t="n">
         <v>110.6</v>
       </c>
     </row>
@@ -14118,6 +14238,21 @@
         <v>13.1</v>
       </c>
       <c r="F8" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K8" s="13" t="n">
         <v>112.6</v>
       </c>
     </row>
@@ -14140,6 +14275,21 @@
         <v>9.5</v>
       </c>
       <c r="F9" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K9" s="13" t="n">
         <v>127.3</v>
       </c>
     </row>
@@ -14162,6 +14312,21 @@
         <v>3.3</v>
       </c>
       <c r="F10" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="K10" s="13" t="n">
         <v>101</v>
       </c>
     </row>
@@ -14184,6 +14349,21 @@
         <v>4.1</v>
       </c>
       <c r="F11" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>117</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="K11" s="13" t="n">
         <v>150.1</v>
       </c>
     </row>
@@ -14206,6 +14386,21 @@
         <v>32.8</v>
       </c>
       <c r="F12" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>137</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K12" s="13" t="n">
         <v>142</v>
       </c>
     </row>
@@ -14228,6 +14423,21 @@
         <v>5.1</v>
       </c>
       <c r="F13" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="K13" s="13" t="n">
         <v>137.3</v>
       </c>
     </row>
@@ -14250,6 +14460,21 @@
         <v>17.7</v>
       </c>
       <c r="F14" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>222.1</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>187.3</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K14" s="13" t="n">
         <v>321.8</v>
       </c>
     </row>
@@ -14272,6 +14497,21 @@
         <v>3.8</v>
       </c>
       <c r="F15" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="K15" s="13" t="n">
         <v>283.2</v>
       </c>
     </row>
@@ -14294,6 +14534,21 @@
         <v>16.9</v>
       </c>
       <c r="F16" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K16" s="13" t="n">
         <v>318.5</v>
       </c>
     </row>
@@ -14316,6 +14571,21 @@
         <v>16.7</v>
       </c>
       <c r="F17" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>370.4</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" s="13" t="n">
         <v>223.6</v>
       </c>
     </row>
@@ -14338,6 +14608,21 @@
         <v>6.6</v>
       </c>
       <c r="F18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>373</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="K18" s="13" t="n">
         <v>282.7</v>
       </c>
     </row>
@@ -14360,6 +14645,21 @@
         <v>46.3</v>
       </c>
       <c r="F19" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="K19" s="13" t="n">
         <v>279.3</v>
       </c>
     </row>
@@ -14382,6 +14682,21 @@
         <v>3.5</v>
       </c>
       <c r="F20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="K20" s="13" t="n">
         <v>165.1</v>
       </c>
     </row>
@@ -14404,6 +14719,21 @@
         <v>6.7</v>
       </c>
       <c r="F21" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>254.7</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K21" s="13" t="n">
         <v>125.3</v>
       </c>
     </row>
@@ -14426,6 +14756,21 @@
         <v>4.4</v>
       </c>
       <c r="F22" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>223</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="K22" s="13" t="n">
         <v>123.8</v>
       </c>
     </row>
@@ -14448,6 +14793,21 @@
         <v>3.1</v>
       </c>
       <c r="F23" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>231.4</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>140.1</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="K23" s="13" t="n">
         <v>157.2</v>
       </c>
     </row>
@@ -14470,6 +14830,21 @@
         <v>8.1</v>
       </c>
       <c r="F24" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>292.3</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="K24" s="13" t="n">
         <v>214.1</v>
       </c>
     </row>
@@ -14492,6 +14867,21 @@
         <v>16.6</v>
       </c>
       <c r="F25" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>320</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K25" s="13" t="n">
         <v>179.3</v>
       </c>
     </row>
@@ -14514,6 +14904,21 @@
         <v>3.7</v>
       </c>
       <c r="F26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>81</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>339.4</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>136.2</v>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="K26" s="13" t="n">
         <v>276.9</v>
       </c>
     </row>
@@ -14536,6 +14941,21 @@
         <v>54</v>
       </c>
       <c r="F27" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="J27" s="13" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="K27" s="13" t="n">
         <v>313.4</v>
       </c>
     </row>
@@ -14558,6 +14978,21 @@
         <v>4.6</v>
       </c>
       <c r="F28" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>478.4</v>
+      </c>
+      <c r="I28" s="13" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="K28" s="13" t="n">
         <v>222.4</v>
       </c>
     </row>
@@ -14580,6 +15015,21 @@
         <v>9.199999999999999</v>
       </c>
       <c r="F29" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>509.9</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>155</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="K29" s="13" t="n">
         <v>227</v>
       </c>
     </row>
@@ -14602,6 +15052,21 @@
         <v>61.9</v>
       </c>
       <c r="F30" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>522.8</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="K30" s="13" t="n">
         <v>226.7</v>
       </c>
     </row>
@@ -14624,6 +15089,21 @@
         <v>5</v>
       </c>
       <c r="F31" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>499.1</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="K31" s="13" t="n">
         <v>192.4</v>
       </c>
     </row>
@@ -14646,6 +15126,21 @@
         <v>5.3</v>
       </c>
       <c r="F32" s="13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>242.2</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>641.6</v>
+      </c>
+      <c r="I32" s="13" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="K32" s="13" t="n">
         <v>440.5</v>
       </c>
     </row>
@@ -14668,6 +15163,21 @@
         <v>16.2</v>
       </c>
       <c r="F33" s="13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>731.5</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K33" s="13" t="n">
         <v>319</v>
       </c>
     </row>
@@ -14690,6 +15200,21 @@
         <v>8.1</v>
       </c>
       <c r="F34" s="13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>765.3</v>
+      </c>
+      <c r="I34" s="13" t="n">
+        <v>150.7</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="K34" s="13" t="n">
         <v>290.7</v>
       </c>
     </row>
@@ -14807,13 +15332,13 @@
         <v>24930.9</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0</v>
+        <v>66404.10000000001</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0</v>
+        <v>12.99</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>12.88</v>
@@ -15002,13 +15527,13 @@
         <v>8994.6</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0</v>
+        <v>16640.1</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0</v>
+        <v>17.94</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>7.28</v>
@@ -15275,13 +15800,13 @@
         <v>2236.2</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0</v>
+        <v>1109.2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0</v>
+        <v>42.72</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1.09</v>
@@ -15392,10 +15917,10 @@
         <v>2720</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0</v>
+        <v>4161.6</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n">
@@ -15541,13 +16066,13 @@
         <v>8501</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>9298.1</v>
+        <v>16640.1</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>23.09</v>
+        <v>25.66</v>
       </c>
       <c r="G25" s="1" t="n">
         <v>7.28</v>
@@ -16979,7 +17504,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>investing.com</t>
+          <t>Cache lần chạy trước (2026-07-11 21:45)</t>
         </is>
       </c>
     </row>
